--- a/2026/CABRERA/ENERO/ENERO CABRERA.xlsx
+++ b/2026/CABRERA/ENERO/ENERO CABRERA.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\2026\CABRERA\ENERO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD4A89EA-EC8C-4453-BE05-A711E2BA8B7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{499885BB-ABE8-401C-8208-9F08FAA21580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
     <sheet name="PRORRATEO" sheetId="2" r:id="rId2"/>
+    <sheet name="anotaciones" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$O$26</definedName>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="135">
   <si>
     <t>TOTAL SUELDO</t>
   </si>
@@ -421,6 +422,18 @@
   </si>
   <si>
     <t>MEDIOS DE CONTACTOS: cabrera140rc@gmail.com  - INFORMAR CUALQUIER TIPO DE PAGO POR ALLI</t>
+  </si>
+  <si>
+    <t>el 2c abono 119447,13 el 20/01 - la pusimos no didentificada, este mes debe abonar $77.374,09</t>
+  </si>
+  <si>
+    <t>Melisa Belmonte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">franco attolino </t>
+  </si>
+  <si>
+    <t>el 1B abono 80500 en enero - la pusimos no didentificada, este mes debe abonar $$92.551,04</t>
   </si>
 </sst>
 </file>
@@ -609,7 +622,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -676,6 +689,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="30">
     <border>
@@ -1036,7 +1061,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="175">
+  <cellXfs count="184">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1279,6 +1304,54 @@
     <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1288,9 +1361,6 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1300,9 +1370,6 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1318,48 +1385,23 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="19" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="19" fillId="13" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -2332,7 +2374,7 @@
       </c>
       <c r="B82" s="32">
         <f>PRORRATEO!G18</f>
-        <v>833585.10000000009</v>
+        <v>914085.10000000009</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2374,7 +2416,7 @@
       </c>
       <c r="B87" s="93">
         <f>SUM(B81:B86)</f>
-        <v>452345.39999999991</v>
+        <v>532845.39999999991</v>
       </c>
       <c r="D87" s="34"/>
     </row>
@@ -2480,26 +2522,26 @@
   <sheetData>
     <row r="1" spans="1:18" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
-      <c r="B1" s="165" t="str">
+      <c r="B1" s="152" t="str">
         <f>RESUMEN!A4</f>
         <v>Banco: Santander
 C.U.I.T.   30-71774143-5
 CBU: 0720533020000000956840 ALIAS: BLONDA.LAGO.CORO
 Nº de cuenta: 533-009568/4</v>
       </c>
-      <c r="C1" s="166"/>
-      <c r="D1" s="166"/>
-      <c r="E1" s="167"/>
-      <c r="F1" s="165" t="s">
+      <c r="C1" s="153"/>
+      <c r="D1" s="153"/>
+      <c r="E1" s="154"/>
+      <c r="F1" s="152" t="s">
         <v>130</v>
       </c>
-      <c r="G1" s="166"/>
-      <c r="H1" s="166"/>
-      <c r="I1" s="167"/>
-      <c r="J1" s="161" t="s">
+      <c r="G1" s="153"/>
+      <c r="H1" s="153"/>
+      <c r="I1" s="154"/>
+      <c r="J1" s="148" t="s">
         <v>122</v>
       </c>
-      <c r="K1" s="162"/>
+      <c r="K1" s="149"/>
       <c r="L1" s="136" t="s">
         <v>123</v>
       </c>
@@ -2512,16 +2554,16 @@
     </row>
     <row r="2" spans="1:18" ht="43.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
-      <c r="B2" s="168"/>
-      <c r="C2" s="169"/>
-      <c r="D2" s="169"/>
-      <c r="E2" s="170"/>
-      <c r="F2" s="168"/>
-      <c r="G2" s="169"/>
-      <c r="H2" s="169"/>
-      <c r="I2" s="170"/>
-      <c r="J2" s="163"/>
-      <c r="K2" s="164"/>
+      <c r="B2" s="155"/>
+      <c r="C2" s="156"/>
+      <c r="D2" s="156"/>
+      <c r="E2" s="157"/>
+      <c r="F2" s="155"/>
+      <c r="G2" s="156"/>
+      <c r="H2" s="156"/>
+      <c r="I2" s="157"/>
+      <c r="J2" s="150"/>
+      <c r="K2" s="151"/>
       <c r="L2" s="137" t="s">
         <v>124</v>
       </c>
@@ -2530,72 +2572,72 @@
       <c r="O2" s="131"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="171" t="s">
+      <c r="A3" s="158" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="173" t="s">
+      <c r="B3" s="160" t="s">
         <v>61</v>
       </c>
-      <c r="C3" s="151" t="s">
+      <c r="C3" s="162" t="s">
         <v>62</v>
       </c>
-      <c r="D3" s="151" t="s">
+      <c r="D3" s="162" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="151" t="s">
+      <c r="E3" s="162" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="151" t="s">
+      <c r="F3" s="162" t="s">
         <v>46</v>
       </c>
-      <c r="G3" s="151" t="s">
+      <c r="G3" s="162" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="151" t="s">
+      <c r="H3" s="162" t="s">
         <v>35</v>
       </c>
-      <c r="I3" s="156" t="s">
+      <c r="I3" s="170" t="s">
         <v>36</v>
       </c>
-      <c r="J3" s="153" t="s">
+      <c r="J3" s="168" t="s">
         <v>34</v>
       </c>
-      <c r="K3" s="153" t="s">
+      <c r="K3" s="168" t="s">
         <v>7</v>
       </c>
-      <c r="L3" s="153" t="s">
+      <c r="L3" s="168" t="s">
         <v>33</v>
       </c>
-      <c r="M3" s="159" t="s">
+      <c r="M3" s="173" t="s">
         <v>44</v>
       </c>
       <c r="N3" s="46" t="s">
         <v>43</v>
       </c>
-      <c r="O3" s="148" t="s">
+      <c r="O3" s="164" t="s">
         <v>42</v>
       </c>
       <c r="R3" s="34"/>
     </row>
     <row r="4" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="172"/>
-      <c r="B4" s="174"/>
-      <c r="C4" s="155"/>
-      <c r="D4" s="155"/>
-      <c r="E4" s="152"/>
-      <c r="F4" s="155"/>
-      <c r="G4" s="155"/>
-      <c r="H4" s="152"/>
-      <c r="I4" s="157"/>
-      <c r="J4" s="154"/>
-      <c r="K4" s="158"/>
-      <c r="L4" s="154"/>
-      <c r="M4" s="160"/>
+      <c r="A4" s="159"/>
+      <c r="B4" s="161"/>
+      <c r="C4" s="163"/>
+      <c r="D4" s="163"/>
+      <c r="E4" s="167"/>
+      <c r="F4" s="163"/>
+      <c r="G4" s="163"/>
+      <c r="H4" s="167"/>
+      <c r="I4" s="171"/>
+      <c r="J4" s="169"/>
+      <c r="K4" s="172"/>
+      <c r="L4" s="169"/>
+      <c r="M4" s="174"/>
       <c r="N4" s="44" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 16/02</v>
       </c>
-      <c r="O4" s="149"/>
+      <c r="O4" s="165"/>
     </row>
     <row r="5" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
@@ -2709,22 +2751,22 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="183" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="122" t="s">
+      <c r="B7" s="123" t="s">
         <v>69</v>
       </c>
-      <c r="C7" s="122" t="s">
+      <c r="C7" s="123" t="s">
         <v>70</v>
       </c>
-      <c r="D7" s="122" t="s">
+      <c r="D7" s="123" t="s">
         <v>71</v>
       </c>
-      <c r="E7" s="125">
+      <c r="E7" s="124">
         <v>6.75</v>
       </c>
-      <c r="F7" s="53">
+      <c r="F7" s="54">
         <v>73279.649999999994</v>
       </c>
       <c r="G7" s="54">
@@ -2771,30 +2813,32 @@
       <c r="A8" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="122" t="s">
+      <c r="B8" s="179" t="s">
         <v>72</v>
       </c>
-      <c r="C8" s="122" t="s">
+      <c r="C8" s="179" t="s">
         <v>73</v>
       </c>
-      <c r="D8" s="122" t="s">
+      <c r="D8" s="179" t="s">
         <v>74</v>
       </c>
-      <c r="E8" s="125">
+      <c r="E8" s="180">
         <v>7.41</v>
       </c>
-      <c r="F8" s="53">
+      <c r="F8" s="181">
         <v>80426.179999999993</v>
       </c>
-      <c r="G8" s="54"/>
+      <c r="G8" s="54">
+        <v>80500</v>
+      </c>
       <c r="H8" s="55"/>
       <c r="I8" s="56">
         <f t="shared" si="4"/>
-        <v>80426.179999999993</v>
+        <v>-73.820000000006985</v>
       </c>
       <c r="J8" s="56">
         <f t="shared" si="5"/>
-        <v>2372.57231</v>
+        <v>0</v>
       </c>
       <c r="K8" s="57">
         <f t="shared" si="0"/>
@@ -2809,15 +2853,18 @@
       </c>
       <c r="N8" s="59">
         <f t="shared" si="6"/>
-        <v>175424.04</v>
+        <v>92551.039999999994</v>
       </c>
       <c r="O8" s="60">
         <f t="shared" si="2"/>
-        <v>180687.04</v>
+        <v>95328.04</v>
       </c>
       <c r="P8" s="34">
         <f t="shared" si="7"/>
         <v>0.04</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>133</v>
       </c>
       <c r="R8" s="34"/>
     </row>
@@ -3048,22 +3095,22 @@
       <c r="A13" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="122" t="s">
+      <c r="B13" s="175" t="s">
         <v>87</v>
       </c>
-      <c r="C13" s="122" t="s">
+      <c r="C13" s="175" t="s">
         <v>88</v>
       </c>
-      <c r="D13" s="122" t="s">
+      <c r="D13" s="175" t="s">
         <v>89</v>
       </c>
-      <c r="E13" s="125">
+      <c r="E13" s="176">
         <v>7.62</v>
       </c>
-      <c r="F13" s="53">
+      <c r="F13" s="177">
         <v>101571.58</v>
       </c>
-      <c r="G13" s="54"/>
+      <c r="G13" s="177"/>
       <c r="H13" s="55"/>
       <c r="I13" s="56">
         <f t="shared" si="4"/>
@@ -3095,6 +3142,9 @@
       <c r="P13" s="34">
         <f t="shared" si="7"/>
         <v>0.09</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -3299,7 +3349,7 @@
       </c>
       <c r="G18" s="45">
         <f>SUM(G5:G17)</f>
-        <v>833585.10000000009</v>
+        <v>914085.10000000009</v>
       </c>
       <c r="H18" s="45">
         <f>SUM(H5:H17)</f>
@@ -3321,105 +3371,98 @@
       </c>
       <c r="N18" s="65">
         <f>SUM(N5:N17)</f>
-        <v>2103802.7800000007</v>
+        <v>2020929.7800000003</v>
       </c>
       <c r="O18" s="65">
         <f>SUM(O5:O17)</f>
-        <v>2166916.7800000007</v>
+        <v>2081557.7800000003</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="D19" s="38"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="D20" s="150" t="s">
+      <c r="D20" s="166" t="s">
         <v>57</v>
       </c>
-      <c r="E20" s="150"/>
-      <c r="F20" s="150"/>
-      <c r="G20" s="150"/>
-      <c r="H20" s="150"/>
-      <c r="I20" s="150"/>
-      <c r="J20" s="150"/>
-      <c r="K20" s="150"/>
-      <c r="L20" s="150"/>
-      <c r="M20" s="150"/>
-      <c r="N20" s="150"/>
+      <c r="E20" s="166"/>
+      <c r="F20" s="166"/>
+      <c r="G20" s="166"/>
+      <c r="H20" s="166"/>
+      <c r="I20" s="166"/>
+      <c r="J20" s="166"/>
+      <c r="K20" s="166"/>
+      <c r="L20" s="166"/>
+      <c r="M20" s="166"/>
+      <c r="N20" s="166"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="D21" s="150"/>
-      <c r="E21" s="150"/>
-      <c r="F21" s="150"/>
-      <c r="G21" s="150"/>
-      <c r="H21" s="150"/>
-      <c r="I21" s="150"/>
-      <c r="J21" s="150"/>
-      <c r="K21" s="150"/>
-      <c r="L21" s="150"/>
-      <c r="M21" s="150"/>
-      <c r="N21" s="150"/>
+      <c r="D21" s="166"/>
+      <c r="E21" s="166"/>
+      <c r="F21" s="166"/>
+      <c r="G21" s="166"/>
+      <c r="H21" s="166"/>
+      <c r="I21" s="166"/>
+      <c r="J21" s="166"/>
+      <c r="K21" s="166"/>
+      <c r="L21" s="166"/>
+      <c r="M21" s="166"/>
+      <c r="N21" s="166"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="D22" s="150"/>
-      <c r="E22" s="150"/>
-      <c r="F22" s="150"/>
-      <c r="G22" s="150"/>
-      <c r="H22" s="150"/>
-      <c r="I22" s="150"/>
-      <c r="J22" s="150"/>
-      <c r="K22" s="150"/>
-      <c r="L22" s="150"/>
-      <c r="M22" s="150"/>
-      <c r="N22" s="150"/>
+      <c r="D22" s="166"/>
+      <c r="E22" s="166"/>
+      <c r="F22" s="166"/>
+      <c r="G22" s="166"/>
+      <c r="H22" s="166"/>
+      <c r="I22" s="166"/>
+      <c r="J22" s="166"/>
+      <c r="K22" s="166"/>
+      <c r="L22" s="166"/>
+      <c r="M22" s="166"/>
+      <c r="N22" s="166"/>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="D23" s="150"/>
-      <c r="E23" s="150"/>
-      <c r="F23" s="150"/>
-      <c r="G23" s="150"/>
-      <c r="H23" s="150"/>
-      <c r="I23" s="150"/>
-      <c r="J23" s="150"/>
-      <c r="K23" s="150"/>
-      <c r="L23" s="150"/>
-      <c r="M23" s="150"/>
-      <c r="N23" s="150"/>
+      <c r="D23" s="166"/>
+      <c r="E23" s="166"/>
+      <c r="F23" s="166"/>
+      <c r="G23" s="166"/>
+      <c r="H23" s="166"/>
+      <c r="I23" s="166"/>
+      <c r="J23" s="166"/>
+      <c r="K23" s="166"/>
+      <c r="L23" s="166"/>
+      <c r="M23" s="166"/>
+      <c r="N23" s="166"/>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="D24" s="150"/>
-      <c r="E24" s="150"/>
-      <c r="F24" s="150"/>
-      <c r="G24" s="150"/>
-      <c r="H24" s="150"/>
-      <c r="I24" s="150"/>
-      <c r="J24" s="150"/>
-      <c r="K24" s="150"/>
-      <c r="L24" s="150"/>
-      <c r="M24" s="150"/>
-      <c r="N24" s="150"/>
+      <c r="D24" s="166"/>
+      <c r="E24" s="166"/>
+      <c r="F24" s="166"/>
+      <c r="G24" s="166"/>
+      <c r="H24" s="166"/>
+      <c r="I24" s="166"/>
+      <c r="J24" s="166"/>
+      <c r="K24" s="166"/>
+      <c r="L24" s="166"/>
+      <c r="M24" s="166"/>
+      <c r="N24" s="166"/>
     </row>
     <row r="25" spans="1:16" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D25" s="150"/>
-      <c r="E25" s="150"/>
-      <c r="F25" s="150"/>
-      <c r="G25" s="150"/>
-      <c r="H25" s="150"/>
-      <c r="I25" s="150"/>
-      <c r="J25" s="150"/>
-      <c r="K25" s="150"/>
-      <c r="L25" s="150"/>
-      <c r="M25" s="150"/>
-      <c r="N25" s="150"/>
+      <c r="D25" s="166"/>
+      <c r="E25" s="166"/>
+      <c r="F25" s="166"/>
+      <c r="G25" s="166"/>
+      <c r="H25" s="166"/>
+      <c r="I25" s="166"/>
+      <c r="J25" s="166"/>
+      <c r="K25" s="166"/>
+      <c r="L25" s="166"/>
+      <c r="M25" s="166"/>
+      <c r="N25" s="166"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="J1:K2"/>
-    <mergeCell ref="B1:E2"/>
-    <mergeCell ref="F1:I2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="D20:N25"/>
     <mergeCell ref="H3:H4"/>
@@ -3431,8 +3474,35 @@
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="E3:E4"/>
+    <mergeCell ref="J1:K2"/>
+    <mergeCell ref="B1:E2"/>
+    <mergeCell ref="F1:I2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3E9F1C8-DABE-4F17-BF70-F15A1A832000}">
+  <dimension ref="C4:C7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="4" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C4" s="178" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="7" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C7" s="182" t="s">
+        <v>134</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>